--- a/Figures/trial_table.xlsx
+++ b/Figures/trial_table.xlsx
@@ -1,20 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="5000000"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://qmulprod-my.sharepoint.com/personal/qp252593_qmul_ac_uk/Documents/Publication/Vine diameter for colonoscopy/Eversion_tracker/Figures/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_514DF647CE9909A9B477A885E3012D16118A26C5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1710178-15D5-41AE-A44F-6AF27647044D}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Cleaned" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="141" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="110">
   <si>
     <t>Trial</t>
   </si>
@@ -341,13 +348,16 @@
   </si>
   <si>
     <t>Mo / test 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no pressure; </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -361,7 +371,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -369,1134 +379,2456 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="true"/>
-    <col min="2" max="2" width="22.19921875" customWidth="true"/>
-    <col min="3" max="3" width="15.06640625" customWidth="true"/>
-    <col min="4" max="4" width="7.86328125" customWidth="true"/>
-    <col min="5" max="5" width="14" customWidth="true"/>
-    <col min="6" max="6" width="6.796875" customWidth="true"/>
-    <col min="7" max="7" width="18.59765625" customWidth="true"/>
-    <col min="8" max="8" width="16.06640625" customWidth="true"/>
-    <col min="9" max="9" width="15.06640625" customWidth="true"/>
-    <col min="10" max="10" width="103.73046875" customWidth="true"/>
-    <col min="11" max="11" width="16.3984375" customWidth="true"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.08984375" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" customWidth="1"/>
+    <col min="7" max="7" width="18.6328125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="15.08984375" customWidth="1"/>
+    <col min="10" max="10" width="103.7265625" customWidth="1"/>
+    <col min="11" max="11" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>0.68500000000000005</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>0.68500000000000005</v>
       </c>
-      <c r="E2" s="0">
-        <v>90.290000000000006</v>
-      </c>
-      <c r="F2" s="0">
-        <v>90.290000000000006</v>
-      </c>
-      <c r="G2" s="0">
+      <c r="E2">
+        <v>90.29</v>
+      </c>
+      <c r="F2">
+        <v>90.29</v>
+      </c>
+      <c r="G2">
         <v>49.5</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>0.318</v>
       </c>
-      <c r="I2" s="0">
-        <v>26.800000000000001</v>
-      </c>
-      <c r="J2" s="0"/>
-      <c r="K2" s="0" t="s">
+      <c r="I2">
+        <v>26.8</v>
+      </c>
+      <c r="K2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>0.66500000000000004</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>0.66500000000000004</v>
       </c>
-      <c r="E3" s="0"/>
-      <c r="F3" s="0"/>
-      <c r="G3" s="0">
-        <v>61.799999999999997</v>
-      </c>
-      <c r="H3" s="0"/>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0" t="s">
+      <c r="G3">
+        <v>61.8</v>
+      </c>
+      <c r="J3" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4">
         <v>0.22900000000000001</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>0.25800000000000001</v>
       </c>
-      <c r="E4" s="0">
-        <v>87.030000000000001</v>
-      </c>
-      <c r="F4" s="0">
-        <v>90.319999999999993</v>
-      </c>
-      <c r="G4" s="0">
+      <c r="E4">
+        <v>87.03</v>
+      </c>
+      <c r="F4">
+        <v>90.32</v>
+      </c>
+      <c r="G4">
         <v>250</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4">
         <v>0.128</v>
       </c>
-      <c r="I4" s="0"/>
-      <c r="J4" s="0" t="s">
+      <c r="J4" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C5">
         <v>0.83599999999999997</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>0.93700000000000006</v>
       </c>
-      <c r="E5" s="0">
-        <v>87.030000000000001</v>
-      </c>
-      <c r="F5" s="0">
-        <v>98.180000000000007</v>
-      </c>
-      <c r="G5" s="0">
+      <c r="E5">
+        <v>87.03</v>
+      </c>
+      <c r="F5">
+        <v>98.18</v>
+      </c>
+      <c r="G5">
         <v>37.799999999999997</v>
       </c>
-      <c r="H5" s="0"/>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0" t="s">
+      <c r="J5" t="s">
         <v>68</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="D6" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="E6" s="0">
+      <c r="C6">
+        <v>0.7</v>
+      </c>
+      <c r="D6">
+        <v>0.7</v>
+      </c>
+      <c r="E6">
         <v>91</v>
       </c>
-      <c r="F6" s="0">
+      <c r="F6">
         <v>91</v>
       </c>
-      <c r="G6" s="0">
-        <v>351.19999999999999</v>
-      </c>
-      <c r="H6" s="0"/>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0" t="s">
+      <c r="G6">
+        <v>351.2</v>
+      </c>
+      <c r="J6" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C7">
         <v>0.48399999999999999</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>0.48399999999999999</v>
       </c>
-      <c r="E7" s="0">
-        <v>95.700000000000003</v>
-      </c>
-      <c r="F7" s="0">
-        <v>95.700000000000003</v>
-      </c>
-      <c r="G7" s="0">
+      <c r="E7">
+        <v>95.7</v>
+      </c>
+      <c r="F7">
+        <v>95.7</v>
+      </c>
+      <c r="G7">
         <v>155.30000000000001</v>
       </c>
-      <c r="H7" s="0"/>
-      <c r="I7" s="0"/>
-      <c r="J7" s="0" t="s">
+      <c r="J7" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C8">
         <v>0.95399999999999996</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>0.95399999999999996</v>
       </c>
-      <c r="E8" s="0">
-        <v>90.540000000000006</v>
-      </c>
-      <c r="F8" s="0">
-        <v>90.540000000000006</v>
-      </c>
-      <c r="G8" s="0">
-        <v>22.300000000000001</v>
-      </c>
-      <c r="H8" s="0"/>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0" t="s">
+      <c r="E8">
+        <v>90.54</v>
+      </c>
+      <c r="F8">
+        <v>90.54</v>
+      </c>
+      <c r="G8">
+        <v>22.3</v>
+      </c>
+      <c r="J8" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="K8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C9">
         <v>0.75</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>0.75</v>
       </c>
-      <c r="E9" s="0">
-        <v>90.030000000000001</v>
-      </c>
-      <c r="F9" s="0">
-        <v>90.030000000000001</v>
-      </c>
-      <c r="G9" s="0">
-        <v>66.299999999999997</v>
-      </c>
-      <c r="H9" s="0"/>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0" t="s">
+      <c r="E9">
+        <v>90.03</v>
+      </c>
+      <c r="F9">
+        <v>90.03</v>
+      </c>
+      <c r="G9">
+        <v>66.3</v>
+      </c>
+      <c r="J9" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="0" t="s">
+      <c r="K9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0">
-        <v>0.67000000000000004</v>
-      </c>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0">
+      <c r="D10">
+        <v>0.67</v>
+      </c>
+      <c r="F10">
         <v>91.25</v>
       </c>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-      <c r="I10" s="0"/>
-      <c r="J10" s="0" t="s">
+      <c r="J10" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="0" t="s">
+      <c r="K10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>1.0069999999999999</v>
       </c>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0">
+      <c r="F11">
         <v>95.5</v>
       </c>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0">
+      <c r="H11">
         <v>0.32700000000000001</v>
       </c>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0" t="s">
+      <c r="J11" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="0" t="s">
+      <c r="K11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="0">
+      <c r="C12">
         <v>1.869</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>1.869</v>
       </c>
-      <c r="E12" s="0">
-        <v>35.240000000000002</v>
-      </c>
-      <c r="F12" s="0">
-        <v>35.240000000000002</v>
-      </c>
-      <c r="G12" s="0">
-        <v>147.40000000000001</v>
-      </c>
-      <c r="H12" s="0"/>
-      <c r="I12" s="0"/>
-      <c r="J12" s="0" t="s">
+      <c r="E12">
+        <v>35.24</v>
+      </c>
+      <c r="F12">
+        <v>35.24</v>
+      </c>
+      <c r="G12">
+        <v>147.4</v>
+      </c>
+      <c r="J12" t="s">
         <v>68</v>
       </c>
-      <c r="K12" s="0" t="s">
+      <c r="K12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="0">
-        <v>1.0800000000000001</v>
-      </c>
-      <c r="D13" s="0">
+      <c r="C13">
+        <v>1.08</v>
+      </c>
+      <c r="D13">
         <v>2.738</v>
       </c>
-      <c r="E13" s="0">
-        <v>34.600000000000001</v>
-      </c>
-      <c r="F13" s="0">
-        <v>45.390000000000001</v>
-      </c>
-      <c r="G13" s="0">
-        <v>132.90000000000001</v>
-      </c>
-      <c r="H13" s="0">
+      <c r="E13">
+        <v>34.6</v>
+      </c>
+      <c r="F13">
+        <v>45.39</v>
+      </c>
+      <c r="G13">
+        <v>132.9</v>
+      </c>
+      <c r="H13">
         <v>0.51200000000000001</v>
       </c>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0" t="s">
+      <c r="J13" t="s">
         <v>67</v>
       </c>
-      <c r="K13" s="0" t="s">
+      <c r="K13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>2.5710000000000002</v>
       </c>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0">
-        <v>104.40000000000001</v>
-      </c>
-      <c r="H14" s="0">
+      <c r="G14">
+        <v>104.4</v>
+      </c>
+      <c r="H14">
         <v>0.54800000000000004</v>
       </c>
-      <c r="I14" s="0">
+      <c r="I14">
         <v>25</v>
       </c>
-      <c r="J14" s="0" t="s">
+      <c r="J14" t="s">
         <v>71</v>
       </c>
-      <c r="K14" s="0" t="s">
+      <c r="K14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="0">
+      <c r="C15">
         <v>2.2400000000000002</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>2.2400000000000002</v>
       </c>
-      <c r="E15" s="0">
-        <v>45.130000000000003</v>
-      </c>
-      <c r="F15" s="0">
-        <v>45.130000000000003</v>
-      </c>
-      <c r="G15" s="0">
-        <v>357.80000000000001</v>
-      </c>
-      <c r="H15" s="0">
+      <c r="E15">
+        <v>45.13</v>
+      </c>
+      <c r="F15">
+        <v>45.13</v>
+      </c>
+      <c r="G15">
+        <v>357.8</v>
+      </c>
+      <c r="H15">
         <v>1.9350000000000001</v>
       </c>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0" t="s">
+      <c r="J15" t="s">
         <v>67</v>
       </c>
-      <c r="K15" s="0" t="s">
+      <c r="K15" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="0">
+      <c r="C16">
         <v>1.6819999999999999</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>2.0539999999999998</v>
       </c>
-      <c r="E16" s="0">
-        <v>36.170000000000002</v>
-      </c>
-      <c r="F16" s="0">
-        <v>50.600000000000001</v>
-      </c>
-      <c r="G16" s="0">
-        <v>107.40000000000001</v>
-      </c>
-      <c r="H16" s="0">
+      <c r="E16">
+        <v>36.17</v>
+      </c>
+      <c r="F16">
+        <v>50.6</v>
+      </c>
+      <c r="G16">
+        <v>107.4</v>
+      </c>
+      <c r="H16">
         <v>0.54500000000000004</v>
       </c>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0" t="s">
+      <c r="J16" t="s">
         <v>67</v>
       </c>
-      <c r="K16" s="0" t="s">
+      <c r="K16" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="0">
+      <c r="C17">
         <v>0.79500000000000004</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>0.79500000000000004</v>
       </c>
-      <c r="E17" s="0">
+      <c r="E17">
         <v>34.630000000000003</v>
       </c>
-      <c r="F17" s="0">
+      <c r="F17">
         <v>47</v>
       </c>
-      <c r="G17" s="0">
+      <c r="G17">
         <v>104</v>
       </c>
-      <c r="H17" s="0">
-        <v>0.35799999999999999</v>
-      </c>
-      <c r="I17" s="0">
-        <v>20.199999999999999</v>
-      </c>
-      <c r="J17" s="0"/>
-      <c r="K17" s="0" t="s">
+      <c r="H17">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="I17">
+        <v>20.2</v>
+      </c>
+      <c r="K17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="0">
+      <c r="C18">
         <v>1.9970000000000001</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>2.633</v>
       </c>
-      <c r="E18" s="0">
-        <v>40.590000000000004</v>
-      </c>
-      <c r="F18" s="0">
-        <v>50.600000000000001</v>
-      </c>
-      <c r="G18" s="0">
+      <c r="E18">
+        <v>40.590000000000003</v>
+      </c>
+      <c r="F18">
+        <v>50.6</v>
+      </c>
+      <c r="G18">
         <v>118</v>
       </c>
-      <c r="H18" s="0">
+      <c r="H18">
         <v>0.52600000000000002</v>
       </c>
-      <c r="I18" s="0">
-        <v>28.899999999999999</v>
-      </c>
-      <c r="J18" s="0"/>
-      <c r="K18" s="0" t="s">
+      <c r="I18">
+        <v>28.9</v>
+      </c>
+      <c r="K18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="0">
-        <v>0.869</v>
-      </c>
-      <c r="D19" s="0">
+      <c r="C19">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="D19">
         <v>0.93500000000000005</v>
       </c>
-      <c r="E19" s="0">
-        <v>30.120000000000001</v>
-      </c>
-      <c r="F19" s="0">
-        <v>53.020000000000003</v>
-      </c>
-      <c r="G19" s="0">
-        <v>178.19999999999999</v>
-      </c>
-      <c r="H19" s="0">
+      <c r="E19">
+        <v>30.12</v>
+      </c>
+      <c r="F19">
+        <v>53.02</v>
+      </c>
+      <c r="G19">
+        <v>178.2</v>
+      </c>
+      <c r="H19">
         <v>0.45100000000000001</v>
       </c>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0" t="s">
+      <c r="J19" t="s">
         <v>67</v>
       </c>
-      <c r="K19" s="0" t="s">
+      <c r="K19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="0">
+      <c r="C20">
         <v>0.41199999999999998</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>0.41199999999999998</v>
       </c>
-      <c r="E20" s="0">
-        <v>25.550000000000001</v>
-      </c>
-      <c r="F20" s="0">
+      <c r="E20">
+        <v>25.55</v>
+      </c>
+      <c r="F20">
         <v>48.61</v>
       </c>
-      <c r="G20" s="0">
+      <c r="G20">
         <v>98</v>
       </c>
-      <c r="H20" s="0">
+      <c r="H20">
         <v>0.504</v>
       </c>
-      <c r="I20" s="0"/>
-      <c r="J20" s="0" t="s">
+      <c r="J20" t="s">
         <v>67</v>
       </c>
-      <c r="K20" s="0" t="s">
+      <c r="K20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="0">
+      <c r="C21">
         <v>2.2490000000000001</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>2.2490000000000001</v>
       </c>
-      <c r="E21" s="0">
+      <c r="E21">
         <v>20.170000000000002</v>
       </c>
-      <c r="F21" s="0">
-        <v>20.620000000000001</v>
-      </c>
-      <c r="G21" s="0">
-        <v>129.90000000000001</v>
-      </c>
-      <c r="H21" s="0">
+      <c r="F21">
+        <v>20.62</v>
+      </c>
+      <c r="G21">
+        <v>129.9</v>
+      </c>
+      <c r="H21">
         <v>0.42199999999999999</v>
       </c>
-      <c r="I21" s="0"/>
-      <c r="J21" s="0" t="s">
+      <c r="J21" t="s">
         <v>67</v>
       </c>
-      <c r="K21" s="0" t="s">
+      <c r="K21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="0">
+      <c r="C22">
         <v>2.8029999999999999</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>3.5329999999999999</v>
       </c>
-      <c r="E22" s="0">
+      <c r="E22">
         <v>23.16</v>
       </c>
-      <c r="F22" s="0">
+      <c r="F22">
         <v>33.11</v>
       </c>
-      <c r="G22" s="0">
+      <c r="G22">
         <v>65.599999999999994</v>
       </c>
-      <c r="H22" s="0">
+      <c r="H22">
         <v>0.311</v>
       </c>
-      <c r="I22" s="0"/>
-      <c r="J22" s="0" t="s">
+      <c r="J22" t="s">
         <v>67</v>
       </c>
-      <c r="K22" s="0" t="s">
+      <c r="K22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="0">
-        <v>4.6799999999999997</v>
-      </c>
-      <c r="D23" s="0">
-        <v>4.6799999999999997</v>
-      </c>
-      <c r="E23" s="0">
-        <v>34.210000000000001</v>
-      </c>
-      <c r="F23" s="0">
-        <v>34.210000000000001</v>
-      </c>
-      <c r="G23" s="0">
+      <c r="C23">
+        <v>4.68</v>
+      </c>
+      <c r="D23">
+        <v>4.68</v>
+      </c>
+      <c r="E23">
+        <v>34.21</v>
+      </c>
+      <c r="F23">
+        <v>34.21</v>
+      </c>
+      <c r="G23">
         <v>17.100000000000001</v>
       </c>
-      <c r="H23" s="0"/>
-      <c r="I23" s="0"/>
-      <c r="J23" s="0" t="s">
+      <c r="J23" t="s">
         <v>68</v>
       </c>
-      <c r="K23" s="0" t="s">
+      <c r="K23" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C24">
         <v>0.97899999999999998</v>
       </c>
-      <c r="D24" s="0">
-        <v>1.8899999999999999</v>
-      </c>
-      <c r="E24" s="0">
+      <c r="D24">
+        <v>1.89</v>
+      </c>
+      <c r="E24">
         <v>16.82</v>
       </c>
-      <c r="F24" s="0">
-        <v>30.469999999999999</v>
-      </c>
-      <c r="G24" s="0">
-        <v>60.799999999999997</v>
-      </c>
-      <c r="H24" s="0">
+      <c r="F24">
+        <v>30.47</v>
+      </c>
+      <c r="G24">
+        <v>60.8</v>
+      </c>
+      <c r="H24">
         <v>4.2859999999999996</v>
       </c>
-      <c r="I24" s="0"/>
-      <c r="J24" s="0" t="s">
+      <c r="J24" t="s">
         <v>67</v>
       </c>
-      <c r="K24" s="0" t="s">
+      <c r="K24" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C25">
         <v>2.952</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>3.2120000000000002</v>
       </c>
-      <c r="E25" s="0">
-        <v>28.989999999999999</v>
-      </c>
-      <c r="F25" s="0">
-        <v>30.629999999999999</v>
-      </c>
-      <c r="G25" s="0">
+      <c r="E25">
+        <v>28.99</v>
+      </c>
+      <c r="F25">
+        <v>30.63</v>
+      </c>
+      <c r="G25">
         <v>187.1</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H25">
         <v>0.58099999999999996</v>
       </c>
-      <c r="I25" s="0"/>
-      <c r="J25" s="0" t="s">
+      <c r="J25" t="s">
         <v>67</v>
       </c>
-      <c r="K25" s="0" t="s">
+      <c r="K25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="0">
+      <c r="C26">
         <v>2.7360000000000002</v>
       </c>
-      <c r="D26" s="0">
+      <c r="D26">
         <v>2.8029999999999999</v>
       </c>
-      <c r="E26" s="0">
-        <v>20.550000000000001</v>
-      </c>
-      <c r="F26" s="0">
-        <v>32.210000000000001</v>
-      </c>
-      <c r="G26" s="0">
-        <v>31.800000000000001</v>
-      </c>
-      <c r="H26" s="0">
+      <c r="E26">
+        <v>20.55</v>
+      </c>
+      <c r="F26">
+        <v>32.21</v>
+      </c>
+      <c r="G26">
+        <v>31.8</v>
+      </c>
+      <c r="H26">
         <v>0.35199999999999998</v>
       </c>
-      <c r="I26" s="0"/>
-      <c r="J26" s="0" t="s">
+      <c r="J26" t="s">
         <v>67</v>
       </c>
-      <c r="K26" s="0" t="s">
+      <c r="K26" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="0">
+      <c r="C27">
         <v>4.4710000000000001</v>
       </c>
-      <c r="D27" s="0">
+      <c r="D27">
         <v>5.4880000000000004</v>
       </c>
-      <c r="E27" s="0">
-        <v>25.129999999999999</v>
-      </c>
-      <c r="F27" s="0">
-        <v>30.600000000000001</v>
-      </c>
-      <c r="G27" s="0">
-        <v>46.100000000000001</v>
-      </c>
-      <c r="H27" s="0">
-        <v>0.93000000000000005</v>
-      </c>
-      <c r="I27" s="0">
+      <c r="E27">
+        <v>25.13</v>
+      </c>
+      <c r="F27">
+        <v>30.6</v>
+      </c>
+      <c r="G27">
+        <v>46.1</v>
+      </c>
+      <c r="H27">
+        <v>0.93</v>
+      </c>
+      <c r="I27">
         <v>61.5</v>
       </c>
-      <c r="J27" s="0"/>
-      <c r="K27" s="0" t="s">
+      <c r="K27" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="0">
+      <c r="C28">
         <v>0.59399999999999997</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>2.1930000000000001</v>
       </c>
-      <c r="E28" s="0"/>
-      <c r="F28" s="0"/>
-      <c r="G28" s="0">
+      <c r="G28">
         <v>155.80000000000001</v>
       </c>
-      <c r="H28" s="0">
+      <c r="H28">
         <v>0.438</v>
       </c>
-      <c r="I28" s="0">
-        <v>69.200000000000003</v>
-      </c>
-      <c r="J28" s="0" t="s">
+      <c r="I28">
+        <v>69.2</v>
+      </c>
+      <c r="J28" t="s">
         <v>72</v>
       </c>
-      <c r="K28" s="0" t="s">
+      <c r="K28" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="0">
+      <c r="C29">
         <v>0.434</v>
       </c>
-      <c r="D29" s="0">
+      <c r="D29">
         <v>0.59699999999999998</v>
       </c>
-      <c r="E29" s="0"/>
-      <c r="F29" s="0"/>
-      <c r="G29" s="0">
-        <v>189.40000000000001</v>
-      </c>
-      <c r="H29" s="0">
+      <c r="G29">
+        <v>189.4</v>
+      </c>
+      <c r="H29">
         <v>0.55100000000000005</v>
       </c>
-      <c r="I29" s="0">
+      <c r="I29">
         <v>65.099999999999994</v>
       </c>
-      <c r="J29" s="0" t="s">
+      <c r="J29" t="s">
         <v>72</v>
       </c>
-      <c r="K29" s="0" t="s">
+      <c r="K29" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="0">
+      <c r="C30">
         <v>1.113</v>
       </c>
-      <c r="D30" s="0">
+      <c r="D30">
         <v>1.113</v>
       </c>
-      <c r="E30" s="0"/>
-      <c r="F30" s="0"/>
-      <c r="G30" s="0">
+      <c r="G30">
         <v>139.1</v>
       </c>
-      <c r="H30" s="0">
-        <v>0.68000000000000005</v>
-      </c>
-      <c r="I30" s="0">
-        <v>86.099999999999994</v>
-      </c>
-      <c r="J30" s="0" t="s">
+      <c r="H30">
+        <v>0.68</v>
+      </c>
+      <c r="I30">
+        <v>86.1</v>
+      </c>
+      <c r="J30" t="s">
         <v>72</v>
       </c>
-      <c r="K30" s="0" t="s">
+      <c r="K30" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="0">
+      <c r="C31">
         <v>0.84699999999999998</v>
       </c>
-      <c r="D31" s="0">
+      <c r="D31">
         <v>1.484</v>
       </c>
-      <c r="E31" s="0"/>
-      <c r="F31" s="0"/>
-      <c r="G31" s="0">
-        <v>93.900000000000006</v>
-      </c>
-      <c r="H31" s="0">
+      <c r="G31">
+        <v>93.9</v>
+      </c>
+      <c r="H31">
         <v>0.71399999999999997</v>
       </c>
-      <c r="I31" s="0">
+      <c r="I31">
         <v>80.900000000000006</v>
       </c>
-      <c r="J31" s="0" t="s">
+      <c r="J31" t="s">
         <v>72</v>
       </c>
-      <c r="K31" s="0" t="s">
+      <c r="K31" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="0">
+      <c r="C32">
         <v>0.86699999999999999</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>1.5049999999999999</v>
       </c>
-      <c r="E32" s="0"/>
-      <c r="F32" s="0"/>
-      <c r="G32" s="0">
-        <v>107.59999999999999</v>
-      </c>
-      <c r="H32" s="0">
+      <c r="G32">
+        <v>107.6</v>
+      </c>
+      <c r="H32">
         <v>0.70799999999999996</v>
       </c>
-      <c r="I32" s="0"/>
-      <c r="J32" s="0" t="s">
+      <c r="J32" t="s">
         <v>73</v>
       </c>
-      <c r="K32" s="0" t="s">
+      <c r="K32" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="0">
+      <c r="C33">
         <v>0.95899999999999996</v>
       </c>
-      <c r="D33" s="0">
+      <c r="D33">
         <v>2.3319999999999999</v>
       </c>
-      <c r="E33" s="0"/>
-      <c r="F33" s="0"/>
-      <c r="G33" s="0">
-        <v>92.799999999999997</v>
-      </c>
-      <c r="H33" s="0">
+      <c r="G33">
+        <v>92.8</v>
+      </c>
+      <c r="H33">
         <v>0.73399999999999999</v>
       </c>
-      <c r="I33" s="0"/>
-      <c r="J33" s="0" t="s">
+      <c r="J33" t="s">
         <v>73</v>
       </c>
-      <c r="K33" s="0" t="s">
+      <c r="K33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="0">
+      <c r="C34">
         <v>0.52400000000000002</v>
       </c>
-      <c r="D34" s="0">
+      <c r="D34">
         <v>1.5980000000000001</v>
       </c>
-      <c r="E34" s="0"/>
-      <c r="F34" s="0"/>
-      <c r="G34" s="0">
-        <v>113.59999999999999</v>
-      </c>
-      <c r="H34" s="0">
+      <c r="G34">
+        <v>113.6</v>
+      </c>
+      <c r="H34">
         <v>0.51500000000000001</v>
       </c>
-      <c r="I34" s="0">
-        <v>47.399999999999999</v>
-      </c>
-      <c r="J34" s="0" t="s">
+      <c r="I34">
+        <v>47.4</v>
+      </c>
+      <c r="J34" t="s">
         <v>72</v>
       </c>
-      <c r="K34" s="0" t="s">
+      <c r="K34" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="0">
+      <c r="C35">
         <v>0.46200000000000002</v>
       </c>
-      <c r="D35" s="0">
+      <c r="D35">
         <v>2.0619999999999998</v>
       </c>
-      <c r="E35" s="0"/>
-      <c r="F35" s="0"/>
-      <c r="G35" s="0">
+      <c r="G35">
         <v>139</v>
       </c>
-      <c r="H35" s="0">
+      <c r="H35">
         <v>0.35399999999999998</v>
       </c>
-      <c r="I35" s="0">
-        <v>61.700000000000003</v>
-      </c>
-      <c r="J35" s="0" t="s">
+      <c r="I35">
+        <v>61.7</v>
+      </c>
+      <c r="J35" t="s">
         <v>72</v>
       </c>
-      <c r="K35" s="0" t="s">
+      <c r="K35" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15011101-439C-4873-9B6F-2E91DDE9272E}">
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" customWidth="1"/>
+    <col min="5" max="5" width="18.7265625" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" customWidth="1"/>
+    <col min="9" max="9" width="26.26953125" customWidth="1"/>
+    <col min="10" max="10" width="48.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="D2">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="E2">
+        <v>90.29</v>
+      </c>
+      <c r="F2">
+        <v>90.29</v>
+      </c>
+      <c r="G2">
+        <v>49.5</v>
+      </c>
+      <c r="H2">
+        <v>0.318</v>
+      </c>
+      <c r="I2">
+        <v>26.8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="D3">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="G3">
+        <v>61.8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="D4">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="E4">
+        <v>87.03</v>
+      </c>
+      <c r="F4">
+        <v>90.32</v>
+      </c>
+      <c r="G4">
+        <v>250</v>
+      </c>
+      <c r="H4">
+        <v>0.128</v>
+      </c>
+      <c r="J4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="D5">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="E5">
+        <v>87.03</v>
+      </c>
+      <c r="F5">
+        <v>98.18</v>
+      </c>
+      <c r="G5">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="J5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6">
+        <v>0.7</v>
+      </c>
+      <c r="D6">
+        <v>0.7</v>
+      </c>
+      <c r="E6">
+        <v>91</v>
+      </c>
+      <c r="F6">
+        <v>91</v>
+      </c>
+      <c r="G6">
+        <v>351.2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="D7">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="E7">
+        <v>95.7</v>
+      </c>
+      <c r="F7">
+        <v>95.7</v>
+      </c>
+      <c r="G7">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="J7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="D8">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="E8">
+        <v>90.54</v>
+      </c>
+      <c r="F8">
+        <v>90.54</v>
+      </c>
+      <c r="G8">
+        <v>22.3</v>
+      </c>
+      <c r="J8" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>0.75</v>
+      </c>
+      <c r="D9">
+        <v>0.75</v>
+      </c>
+      <c r="E9">
+        <v>90.03</v>
+      </c>
+      <c r="F9">
+        <v>90.03</v>
+      </c>
+      <c r="G9">
+        <v>66.3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>0.67</v>
+      </c>
+      <c r="F10">
+        <v>91.25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="F11">
+        <v>95.5</v>
+      </c>
+      <c r="H11">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="J11" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12">
+        <v>1.869</v>
+      </c>
+      <c r="D12">
+        <v>1.869</v>
+      </c>
+      <c r="E12">
+        <v>35.24</v>
+      </c>
+      <c r="F12">
+        <v>35.24</v>
+      </c>
+      <c r="G12">
+        <v>147.4</v>
+      </c>
+      <c r="J12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13">
+        <v>1.08</v>
+      </c>
+      <c r="D13">
+        <v>2.738</v>
+      </c>
+      <c r="E13">
+        <v>34.6</v>
+      </c>
+      <c r="F13">
+        <v>45.39</v>
+      </c>
+      <c r="G13">
+        <v>132.9</v>
+      </c>
+      <c r="H13">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="J13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14">
+        <v>2.5710000000000002</v>
+      </c>
+      <c r="G14">
+        <v>104.4</v>
+      </c>
+      <c r="H14">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="I14">
+        <v>25</v>
+      </c>
+      <c r="J14" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="D15">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E15">
+        <v>45.13</v>
+      </c>
+      <c r="F15">
+        <v>45.13</v>
+      </c>
+      <c r="G15">
+        <v>357.8</v>
+      </c>
+      <c r="H15">
+        <v>1.9350000000000001</v>
+      </c>
+      <c r="J15" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>1.6819999999999999</v>
+      </c>
+      <c r="D16">
+        <v>2.0539999999999998</v>
+      </c>
+      <c r="E16">
+        <v>36.17</v>
+      </c>
+      <c r="F16">
+        <v>50.6</v>
+      </c>
+      <c r="G16">
+        <v>107.4</v>
+      </c>
+      <c r="H16">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="J16" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="D17">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="E17">
+        <v>34.630000000000003</v>
+      </c>
+      <c r="F17">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>104</v>
+      </c>
+      <c r="H17">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="I17">
+        <v>20.2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18">
+        <v>1.9970000000000001</v>
+      </c>
+      <c r="D18">
+        <v>2.633</v>
+      </c>
+      <c r="E18">
+        <v>40.590000000000003</v>
+      </c>
+      <c r="F18">
+        <v>50.6</v>
+      </c>
+      <c r="G18">
+        <v>118</v>
+      </c>
+      <c r="H18">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="I18">
+        <v>28.9</v>
+      </c>
+      <c r="K18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19">
+        <v>0.86899999999999999</v>
+      </c>
+      <c r="D19">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="E19">
+        <v>30.12</v>
+      </c>
+      <c r="F19">
+        <v>53.02</v>
+      </c>
+      <c r="G19">
+        <v>178.2</v>
+      </c>
+      <c r="H19">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="J19" t="s">
+        <v>67</v>
+      </c>
+      <c r="K19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="D20">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="E20">
+        <v>25.55</v>
+      </c>
+      <c r="F20">
+        <v>48.61</v>
+      </c>
+      <c r="G20">
+        <v>98</v>
+      </c>
+      <c r="H20">
+        <v>0.504</v>
+      </c>
+      <c r="J20" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="D21">
+        <v>2.2490000000000001</v>
+      </c>
+      <c r="E21">
+        <v>20.170000000000002</v>
+      </c>
+      <c r="F21">
+        <v>20.62</v>
+      </c>
+      <c r="G21">
+        <v>129.9</v>
+      </c>
+      <c r="H21">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="J21" t="s">
+        <v>67</v>
+      </c>
+      <c r="K21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <v>2.8029999999999999</v>
+      </c>
+      <c r="D22">
+        <v>3.5329999999999999</v>
+      </c>
+      <c r="E22">
+        <v>23.16</v>
+      </c>
+      <c r="F22">
+        <v>33.11</v>
+      </c>
+      <c r="G22">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="H22">
+        <v>0.311</v>
+      </c>
+      <c r="J22" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <v>4.68</v>
+      </c>
+      <c r="D23">
+        <v>4.68</v>
+      </c>
+      <c r="E23">
+        <v>34.21</v>
+      </c>
+      <c r="F23">
+        <v>34.21</v>
+      </c>
+      <c r="G23">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="J23" t="s">
+        <v>68</v>
+      </c>
+      <c r="K23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="D24">
+        <v>1.89</v>
+      </c>
+      <c r="E24">
+        <v>16.82</v>
+      </c>
+      <c r="F24">
+        <v>30.47</v>
+      </c>
+      <c r="G24">
+        <v>60.8</v>
+      </c>
+      <c r="H24">
+        <v>4.2859999999999996</v>
+      </c>
+      <c r="J24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25">
+        <v>2.952</v>
+      </c>
+      <c r="D25">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="E25">
+        <v>28.99</v>
+      </c>
+      <c r="F25">
+        <v>30.63</v>
+      </c>
+      <c r="G25">
+        <v>187.1</v>
+      </c>
+      <c r="H25">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="J25" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26">
+        <v>2.7360000000000002</v>
+      </c>
+      <c r="D26">
+        <v>2.8029999999999999</v>
+      </c>
+      <c r="E26">
+        <v>20.55</v>
+      </c>
+      <c r="F26">
+        <v>32.21</v>
+      </c>
+      <c r="G26">
+        <v>31.8</v>
+      </c>
+      <c r="H26">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="J26" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27">
+        <v>4.4710000000000001</v>
+      </c>
+      <c r="D27">
+        <v>5.4880000000000004</v>
+      </c>
+      <c r="E27">
+        <v>25.13</v>
+      </c>
+      <c r="F27">
+        <v>30.6</v>
+      </c>
+      <c r="G27">
+        <v>46.1</v>
+      </c>
+      <c r="H27">
+        <v>0.93</v>
+      </c>
+      <c r="I27">
+        <v>61.5</v>
+      </c>
+      <c r="K27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="D28">
+        <v>2.1930000000000001</v>
+      </c>
+      <c r="G28">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="H28">
+        <v>0.438</v>
+      </c>
+      <c r="I28">
+        <v>69</v>
+      </c>
+      <c r="J28" t="s">
+        <v>72</v>
+      </c>
+      <c r="K28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29">
+        <v>0.434</v>
+      </c>
+      <c r="D29">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="G29">
+        <v>189.4</v>
+      </c>
+      <c r="H29">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="I29">
+        <v>65</v>
+      </c>
+      <c r="J29" t="s">
+        <v>72</v>
+      </c>
+      <c r="K29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30">
+        <v>1.113</v>
+      </c>
+      <c r="D30">
+        <v>1.113</v>
+      </c>
+      <c r="G30">
+        <v>139.1</v>
+      </c>
+      <c r="H30">
+        <v>0.68</v>
+      </c>
+      <c r="I30">
+        <v>86</v>
+      </c>
+      <c r="J30" t="s">
+        <v>72</v>
+      </c>
+      <c r="K30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="D31">
+        <v>1.484</v>
+      </c>
+      <c r="G31">
+        <v>93.9</v>
+      </c>
+      <c r="H31">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="I31">
+        <v>81</v>
+      </c>
+      <c r="J31" t="s">
+        <v>72</v>
+      </c>
+      <c r="K31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="D32">
+        <v>1.5049999999999999</v>
+      </c>
+      <c r="G32">
+        <v>107.6</v>
+      </c>
+      <c r="H32">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="I32">
+        <v>103</v>
+      </c>
+      <c r="J32" t="s">
+        <v>109</v>
+      </c>
+      <c r="K32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="D33">
+        <v>2.3319999999999999</v>
+      </c>
+      <c r="G33">
+        <v>92.8</v>
+      </c>
+      <c r="H33">
+        <v>0.73399999999999999</v>
+      </c>
+      <c r="I33">
+        <v>80</v>
+      </c>
+      <c r="J33" t="s">
+        <v>109</v>
+      </c>
+      <c r="K33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="D34">
+        <v>1.5980000000000001</v>
+      </c>
+      <c r="G34">
+        <v>113.6</v>
+      </c>
+      <c r="H34">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="I34">
+        <v>48</v>
+      </c>
+      <c r="J34" t="s">
+        <v>72</v>
+      </c>
+      <c r="K34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="D35">
+        <v>2.0619999999999998</v>
+      </c>
+      <c r="G35">
+        <v>139</v>
+      </c>
+      <c r="H35">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="I35">
+        <v>62</v>
+      </c>
+      <c r="J35" t="s">
+        <v>72</v>
+      </c>
+      <c r="K35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{569df091-b013-40e3-86ee-bd9cb9e25814}" enabled="0" method="" siteId="{569df091-b013-40e3-86ee-bd9cb9e25814}" removed="1"/>
+</clbl:labelList>
 </file>